--- a/docs/Logic Requirements/Ageipelago William Wallace.xlsx
+++ b/docs/Logic Requirements/Ageipelago William Wallace.xlsx
@@ -5,15 +5,22 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb6dd295c338e39f/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{70093AD7-EC08-420A-A45B-C04C0E461DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7260FECD-7FD7-43A7-A0DD-3EEBF584A3F4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B02CA9-6883-4A3E-8AF4-B75F246DDA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1D996FA3-8E71-4AAB-A721-F834CDA60D66}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="893" activeTab="7" xr2:uid="{1D996FA3-8E71-4AAB-A721-F834CDA60D66}"/>
   </bookViews>
   <sheets>
     <sheet name="William Wallace" sheetId="1" r:id="rId1"/>
+    <sheet name="Marching and Fighting" sheetId="2" r:id="rId2"/>
+    <sheet name="Feeding the Army" sheetId="3" r:id="rId3"/>
+    <sheet name="Training the Troops" sheetId="4" r:id="rId4"/>
+    <sheet name="Research and Technology" sheetId="5" r:id="rId5"/>
+    <sheet name="The Battle of Stirling" sheetId="6" r:id="rId6"/>
+    <sheet name="Forge an Alliance" sheetId="7" r:id="rId7"/>
+    <sheet name="The Battle of Falkirk" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="104">
   <si>
     <t>Scenario</t>
   </si>
@@ -577,12 +584,126 @@
     <t>Reaching Castle Age requires Castle Age to be unlocked.
 Building a Castle requires Castle Age and Castles to be unlocked.</t>
   </si>
+  <si>
+    <t>Killable Units</t>
+  </si>
+  <si>
+    <t>Destructible Buildings</t>
+  </si>
+  <si>
+    <t>Deer</t>
+  </si>
+  <si>
+    <t>No items required</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>Sheep</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>Wild Boar</t>
+  </si>
+  <si>
+    <t>Siege Workshop</t>
+  </si>
+  <si>
+    <t>Grey Wolf</t>
+  </si>
+  <si>
+    <t>Lumber Camp</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Town Center</t>
+  </si>
+  <si>
+    <t>Militia</t>
+  </si>
+  <si>
+    <t>Crossbowman</t>
+  </si>
+  <si>
+    <t>Scout Cavalry</t>
+  </si>
+  <si>
+    <t>Mill</t>
+  </si>
+  <si>
+    <t>Archery Range</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Monastery</t>
+  </si>
+  <si>
+    <t>Battering Ram</t>
+  </si>
+  <si>
+    <t>Mining Camp</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>Blacksmith</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>Stone Wall</t>
+  </si>
+  <si>
+    <t>Stone Gate</t>
+  </si>
+  <si>
+    <t>Outpost</t>
+  </si>
+  <si>
+    <t>Watch Tower</t>
+  </si>
+  <si>
+    <t>Galleon</t>
+  </si>
+  <si>
+    <t>Knight</t>
+  </si>
+  <si>
+    <t>Man-at-Arms</t>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>Palisade Wall</t>
+  </si>
+  <si>
+    <t>Spearman</t>
+  </si>
+  <si>
+    <t>Pikeman</t>
+  </si>
+  <si>
+    <t>Longbowman</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -662,6 +783,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -671,7 +811,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -759,11 +899,70 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -818,6 +1017,61 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1308,7 +1562,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" ht="132" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="10" t="s">
         <v>24</v>
       </c>
@@ -1442,4 +1696,2297 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF6A4EDC-A2A6-4384-9D45-5513B4018DE4}">
+  <dimension ref="G1:M42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:13" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+    </row>
+    <row r="5" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+    </row>
+    <row r="6" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+    </row>
+    <row r="7" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+    </row>
+    <row r="8" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+    </row>
+    <row r="9" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+    </row>
+    <row r="10" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+    </row>
+    <row r="11" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+    </row>
+    <row r="12" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+    </row>
+    <row r="13" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="29"/>
+    </row>
+    <row r="14" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="29"/>
+    </row>
+    <row r="15" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="29"/>
+    </row>
+    <row r="16" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="29"/>
+    </row>
+    <row r="17" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="29"/>
+    </row>
+    <row r="18" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="29"/>
+    </row>
+    <row r="19" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="29"/>
+    </row>
+    <row r="20" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="29"/>
+    </row>
+    <row r="21" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="29"/>
+    </row>
+    <row r="22" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="29"/>
+    </row>
+    <row r="23" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="29"/>
+    </row>
+    <row r="24" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="29"/>
+    </row>
+    <row r="25" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="29"/>
+    </row>
+    <row r="26" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="29"/>
+    </row>
+    <row r="27" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="29"/>
+    </row>
+    <row r="28" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="29"/>
+    </row>
+    <row r="29" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="29"/>
+    </row>
+    <row r="30" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+      <c r="M30" s="29"/>
+    </row>
+    <row r="31" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="29"/>
+    </row>
+    <row r="32" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="29"/>
+    </row>
+    <row r="33" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="29"/>
+    </row>
+    <row r="34" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="29"/>
+    </row>
+    <row r="35" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="29"/>
+    </row>
+    <row r="36" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="29"/>
+    </row>
+    <row r="37" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="29"/>
+    </row>
+    <row r="38" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+    </row>
+    <row r="39" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+    </row>
+    <row r="40" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
+    </row>
+    <row r="41" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
+    </row>
+    <row r="42" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE0B8A1-A1CB-49C6-9730-949A4C34C8FA}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF1F63AB-7290-450B-8980-98B8DF63CD4A}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7768BA2-988B-4725-884E-9A32CD20C2E6}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{603586A2-08C1-4762-8104-5B2832D5265D}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="L6" s="23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CDB17CE-ADDF-47FF-AB15-5D9169E4FB09}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="K12" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="K13" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C3B2F3-07FC-4AA1-B938-54EA265CD689}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="K9" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="K10" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="K11" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="K12" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="K13" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="K14" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="K15" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="K16" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="K17" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="K18" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="K19" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="K20" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="L20" s="23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>